--- a/04 - RELATÓRIO DE PAGAMENTO/Tabela.xlsx
+++ b/04 - RELATÓRIO DE PAGAMENTO/Tabela.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\04 - RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28073558-F98A-4DC6-B567-4294A16E261C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A4425-6A97-41DC-86D4-3750311C6B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
   <si>
     <t>CONCESSIONÁRIA - 1º NIVEL</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Deferido</t>
   </si>
   <si>
-    <t>S/I</t>
-  </si>
-  <si>
     <t>Comprovante de pagamento</t>
   </si>
   <si>
@@ -233,55 +230,50 @@
     <t>Respondido</t>
   </si>
   <si>
-    <t>VIGENTE_venc:14/11/2026</t>
-  </si>
-  <si>
-    <t>SÃO JOÃO DO RIO DO PEIXE</t>
-  </si>
-  <si>
-    <t>RECLAMAÇÃO 012/2025</t>
-  </si>
-  <si>
-    <t>Cobrança Indevida - Perdas nos Reatores</t>
-  </si>
-  <si>
-    <t>381428-2</t>
-  </si>
-  <si>
     <t>Em análise na ouvidoria da Aneel</t>
   </si>
   <si>
-    <t>Débora</t>
-  </si>
-  <si>
-    <t>Reeingressado por conta de pendência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">010.585.43825-82 </t>
-  </si>
-  <si>
     <t>Em análise</t>
   </si>
   <si>
-    <t>erro no memorial de cálculo na aplicação do dobro</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Relatório enviado ao parceiro</t>
+    <t>VIGENTE_venc:14/05/2027</t>
+  </si>
+  <si>
+    <t>SÃO MAMEDE</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO 038/2025</t>
+  </si>
+  <si>
+    <t>Cobrança Indevida - Ausência parcela DIC/2</t>
+  </si>
+  <si>
+    <t>Aguardando cálculo</t>
+  </si>
+  <si>
+    <t>Passar para próxima instância</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Arthur</t>
+  </si>
+  <si>
+    <t>010.647.00426-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,18 +323,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -354,12 +334,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -371,14 +345,43 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF393939"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -435,12 +438,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3C7D22"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
@@ -451,8 +448,26 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF275317"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -550,12 +565,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -600,56 +625,71 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -678,12 +718,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1005,41 +1041,41 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="36" t="s">
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="39" t="s">
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="41" t="s">
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
@@ -1241,189 +1277,191 @@
       <c r="AR3" s="9"/>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AU3" s="8" t="s">
+      <c r="AV3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="AW3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="AX3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="BA3" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:54" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>65</v>
+      <c r="A4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>66</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="F4" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="17">
+        <v>454807</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="18">
+        <v>46017</v>
+      </c>
+      <c r="K4" s="18">
+        <v>46127</v>
+      </c>
+      <c r="L4" s="26">
+        <v>1420.86</v>
+      </c>
+      <c r="M4" s="19">
+        <v>46134</v>
+      </c>
+      <c r="N4" s="26">
+        <v>1420.86</v>
+      </c>
+      <c r="O4" s="20">
+        <v>1</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>46014</v>
+      </c>
+      <c r="R4" s="21">
+        <v>902827313</v>
+      </c>
+      <c r="S4" s="19">
+        <v>46017</v>
+      </c>
+      <c r="T4" s="19">
+        <v>46044</v>
+      </c>
+      <c r="U4" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="X4" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="19">
+        <v>46059</v>
+      </c>
+      <c r="Z4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB4" s="19">
+        <v>46127</v>
+      </c>
+      <c r="AC4" s="19">
+        <v>46089</v>
+      </c>
+      <c r="AD4" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="21">
-        <v>45730</v>
-      </c>
-      <c r="K4" s="21">
-        <v>45798</v>
-      </c>
-      <c r="L4" s="31">
-        <v>251214.62</v>
-      </c>
-      <c r="M4" s="22">
-        <v>45852</v>
-      </c>
-      <c r="N4" s="31">
-        <v>251214.62</v>
-      </c>
-      <c r="O4" s="23">
-        <v>1</v>
-      </c>
-      <c r="P4" s="24" t="s">
+      <c r="AE4" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="Q4" s="22">
-        <v>45728</v>
-      </c>
-      <c r="R4" s="25">
-        <v>9569821</v>
-      </c>
-      <c r="S4" s="22">
-        <v>45730</v>
-      </c>
-      <c r="T4" s="22">
-        <v>45758</v>
-      </c>
-      <c r="U4" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" s="15" t="s">
+      <c r="AF4" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="W4" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="X4" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y4" s="22">
-        <v>45737</v>
-      </c>
-      <c r="Z4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA4" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB4" s="22">
-        <v>45749</v>
-      </c>
-      <c r="AC4" s="22">
-        <v>45767</v>
-      </c>
-      <c r="AD4" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF4" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG4" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH4" s="22">
-        <v>45897</v>
+      <c r="AG4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH4" s="19">
+        <v>46227</v>
       </c>
       <c r="AI4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="AK4" s="22">
-        <v>46240</v>
-      </c>
-      <c r="AL4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AO4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP4" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ4" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR4" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS4" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT4" s="22">
-        <v>46245</v>
-      </c>
-      <c r="AU4" s="15"/>
-      <c r="AV4" s="42">
-        <v>23212.31</v>
-      </c>
-      <c r="AW4" s="22">
-        <v>46120</v>
-      </c>
-      <c r="AX4" s="22">
-        <v>46245</v>
-      </c>
-      <c r="AY4" s="32">
-        <v>2738.5</v>
-      </c>
-      <c r="AZ4" s="22">
-        <v>46184</v>
-      </c>
-      <c r="BA4" s="22">
-        <v>46245</v>
-      </c>
-      <c r="BB4" s="1"/>
+      <c r="AJ4" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK4" s="19">
+        <v>46230</v>
+      </c>
+      <c r="AL4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM4" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP4" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AS4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT4" s="19">
+        <v>46283</v>
+      </c>
+      <c r="AU4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AV4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB4" s="37"/>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.3">
       <c r="N12" s="7"/>

--- a/04 - RELATÓRIO DE PAGAMENTO/Tabela.xlsx
+++ b/04 - RELATÓRIO DE PAGAMENTO/Tabela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\04 - RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A4425-6A97-41DC-86D4-3750311C6B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF386BB-0C0F-4DFE-B0B9-2E61B2B055CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>CONCESSIONÁRIA - 1º NIVEL</t>
   </si>
@@ -218,52 +218,40 @@
     <t>Recibo do pagamento ajuste</t>
   </si>
   <si>
-    <t>THAMIRES E RUDÁ</t>
-  </si>
-  <si>
     <t>NÃO</t>
   </si>
   <si>
     <t>Cobrança Indevida</t>
   </si>
   <si>
-    <t>Respondido</t>
-  </si>
-  <si>
-    <t>Em análise na ouvidoria da Aneel</t>
-  </si>
-  <si>
-    <t>Em análise</t>
-  </si>
-  <si>
-    <t>VIGENTE_venc:14/05/2027</t>
-  </si>
-  <si>
-    <t>SÃO MAMEDE</t>
-  </si>
-  <si>
-    <t>RECLAMAÇÃO 038/2025</t>
-  </si>
-  <si>
-    <t>Cobrança Indevida - Ausência parcela DIC/2</t>
-  </si>
-  <si>
-    <t>Aguardando cálculo</t>
-  </si>
-  <si>
-    <t>Passar para próxima instância</t>
-  </si>
-  <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>Arthur</t>
-  </si>
-  <si>
-    <t>010.647.00426-43</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>VALDÉCIO</t>
+  </si>
+  <si>
+    <t>VIGENTE_venc:19/08/2029</t>
+  </si>
+  <si>
+    <t>ARARUNA</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO 002/2025</t>
+  </si>
+  <si>
+    <t>Cobrança Indevida - Enquadramento IP</t>
+  </si>
+  <si>
+    <t>1806543-3</t>
+  </si>
+  <si>
+    <t>Pendente de contestação</t>
+  </si>
+  <si>
+    <t>Arquivado</t>
+  </si>
+  <si>
+    <t>S/I</t>
+  </si>
+  <si>
+    <t>Contestar: Complementar do Dobro. Detalhe: A reclamação havia sido deferida, porém foi interpretada como já corrigida e esquecida.</t>
   </si>
 </sst>
 </file>
@@ -273,7 +261,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,12 +305,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -339,49 +321,37 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF074F69"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <sz val="11"/>
       <color rgb="FF0D0D0D"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C5700"/>
+      <color rgb="FF404040"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF393939"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,12 +390,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCFF"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF8ED973"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
@@ -444,30 +408,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF94DCF8"/>
+        <fgColor rgb="FF808080"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF275317"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF808080"/>
+        <fgColor rgb="FF3C7D22"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -532,45 +484,8 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -580,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -625,97 +540,82 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB12"/>
+  <dimension ref="A1:DG12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
@@ -1025,7 +925,7 @@
     <col min="53" max="53" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1041,47 +941,47 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="38" t="s">
+      <c r="P1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="41" t="s">
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="44" t="s">
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="45"/>
-      <c r="AI1" s="45"/>
-      <c r="AJ1" s="45"/>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="46" t="s">
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
     </row>
-    <row r="2" spans="1:54" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:111" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1218,7 +1118,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:111" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="8"/>
@@ -1301,169 +1201,208 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:54" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>66</v>
+    <row r="4" spans="1:111" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>63</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="J4" s="34">
+        <v>45952</v>
+      </c>
+      <c r="K4" s="16">
+        <v>46286</v>
+      </c>
+      <c r="L4" s="35">
+        <v>24228.31</v>
+      </c>
+      <c r="M4" s="34">
+        <v>46135</v>
+      </c>
+      <c r="N4" s="35">
+        <v>24228.31</v>
+      </c>
+      <c r="O4" s="17">
+        <v>1</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>45945</v>
+      </c>
+      <c r="R4" s="18">
+        <v>195792993</v>
+      </c>
+      <c r="S4" s="16">
+        <v>45952</v>
+      </c>
+      <c r="T4" s="16">
+        <v>46204</v>
+      </c>
+      <c r="U4" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="17">
-        <v>454807</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="18">
-        <v>46017</v>
-      </c>
-      <c r="K4" s="18">
-        <v>46127</v>
-      </c>
-      <c r="L4" s="26">
-        <v>1420.86</v>
-      </c>
-      <c r="M4" s="19">
-        <v>46134</v>
-      </c>
-      <c r="N4" s="26">
-        <v>1420.86</v>
-      </c>
-      <c r="O4" s="20">
-        <v>1</v>
-      </c>
-      <c r="P4" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="19">
-        <v>46014</v>
-      </c>
-      <c r="R4" s="21">
-        <v>902827313</v>
-      </c>
-      <c r="S4" s="19">
-        <v>46017</v>
-      </c>
-      <c r="T4" s="19">
-        <v>46044</v>
-      </c>
-      <c r="U4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="W4" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" s="19">
-        <v>46059</v>
-      </c>
-      <c r="Z4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA4" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB4" s="19">
-        <v>46127</v>
-      </c>
-      <c r="AC4" s="19">
-        <v>46089</v>
-      </c>
-      <c r="AD4" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE4" s="15" t="s">
+      <c r="W4" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="X4" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF4" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO4" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="AF4" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH4" s="19">
-        <v>46227</v>
-      </c>
-      <c r="AI4" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ4" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK4" s="19">
-        <v>46230</v>
-      </c>
-      <c r="AL4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM4" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AO4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP4" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQ4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT4" s="19">
-        <v>46283</v>
-      </c>
-      <c r="AU4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AV4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AW4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB4" s="37"/>
+      <c r="AP4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ4" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR4" s="39"/>
+      <c r="AS4" s="39"/>
+      <c r="AT4" s="40">
+        <v>46286</v>
+      </c>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="39"/>
+      <c r="BC4" s="39"/>
+      <c r="BD4" s="39"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="39"/>
+      <c r="BG4" s="39"/>
+      <c r="BH4" s="39"/>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="39"/>
+      <c r="BL4" s="39"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="39"/>
+      <c r="BQ4" s="39"/>
+      <c r="BR4" s="39"/>
+      <c r="BS4" s="39"/>
+      <c r="BT4" s="39"/>
+      <c r="BU4" s="39"/>
+      <c r="BV4" s="39"/>
+      <c r="BW4" s="39"/>
+      <c r="BX4" s="39"/>
+      <c r="BY4" s="39"/>
+      <c r="BZ4" s="39"/>
+      <c r="CA4" s="39"/>
+      <c r="CB4" s="39"/>
+      <c r="CC4" s="39"/>
+      <c r="CD4" s="39"/>
+      <c r="CE4" s="39"/>
+      <c r="CF4" s="39"/>
+      <c r="CG4" s="39"/>
+      <c r="CH4" s="39"/>
+      <c r="CI4" s="39"/>
+      <c r="CJ4" s="39"/>
+      <c r="CK4" s="39"/>
+      <c r="CL4" s="39"/>
+      <c r="CM4" s="39"/>
+      <c r="CN4" s="39"/>
+      <c r="CO4" s="39"/>
+      <c r="CP4" s="39"/>
+      <c r="CQ4" s="39"/>
+      <c r="CR4" s="39"/>
+      <c r="CS4" s="39"/>
+      <c r="CT4" s="39"/>
+      <c r="CU4" s="39"/>
+      <c r="CV4" s="39"/>
+      <c r="CW4" s="39"/>
+      <c r="CX4" s="39"/>
+      <c r="CY4" s="39"/>
+      <c r="CZ4" s="39"/>
+      <c r="DA4" s="39"/>
+      <c r="DB4" s="39"/>
+      <c r="DC4" s="39"/>
+      <c r="DD4" s="39"/>
+      <c r="DE4" s="39"/>
+      <c r="DF4" s="39"/>
+      <c r="DG4" s="39"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:111" x14ac:dyDescent="0.3">
       <c r="N12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
